--- a/stories/arbres/TREE-SEC-050.xlsx
+++ b/stories/arbres/TREE-SEC-050.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est avec maman, à la ferme. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo écoute maman. Hugo entend les mots : feu vert, main, adulte, trottoir en attendant.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1870,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Attendre le feu vert avec l'adulte.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2047,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo respire. Hugo retient : feu vert, main, adulte, trottoir en attendant. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2238,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2409,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2549,6 +2602,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2717,6 +2775,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2942,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3113,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3280,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3451,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3618,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3789,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3889,6 +3982,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4057,6 +4155,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4219,6 +4322,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4385,6 +4493,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4547,6 +4660,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4713,6 +4831,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4875,6 +4998,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5041,6 +5169,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5229,6 +5362,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5397,6 +5535,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5559,6 +5702,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5725,6 +5873,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5887,6 +6040,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6053,6 +6211,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6215,6 +6378,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6239,7 +6407,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6381,6 +6549,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6565,6 +6739,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Attendre le feu vert avec l'adulte.</t>
         </is>
       </c>
     </row>
@@ -6737,6 +6916,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo respire. Hugo retient : feu vert, main, adulte, trottoir en attendant. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6923,6 +7107,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7089,6 +7278,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7277,6 +7471,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7445,6 +7644,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7607,6 +7811,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7773,6 +7982,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7935,6 +8149,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8101,6 +8320,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8263,6 +8487,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8429,6 +8658,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8617,6 +8851,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8785,6 +9024,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8947,6 +9191,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9113,6 +9362,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9275,6 +9529,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9441,6 +9700,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9603,6 +9867,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9769,6 +10038,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9957,6 +10231,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10125,6 +10404,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10287,6 +10571,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10453,6 +10742,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10615,6 +10909,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10781,6 +11080,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10943,6 +11247,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10967,7 +11276,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On se tient la main. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11109,6 +11418,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : feu vert, main, adulte, trottoir en attendant. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. On se tient la main.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11293,6 +11608,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Attendre le feu vert avec l'adulte.</t>
         </is>
       </c>
     </row>
@@ -11465,6 +11785,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo respire. Hugo retient : feu vert, main, adulte, trottoir en attendant. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11651,6 +11976,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11817,6 +12147,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12005,6 +12340,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12173,6 +12513,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12335,6 +12680,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12501,6 +12851,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12663,6 +13018,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12829,6 +13189,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12991,6 +13356,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13157,6 +13527,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13345,6 +13720,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13513,6 +13893,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13675,6 +14060,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13841,6 +14231,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14003,6 +14398,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14169,6 +14569,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14331,6 +14736,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14497,6 +14907,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14685,6 +15100,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14853,6 +15273,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15015,6 +15440,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15181,6 +15611,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15343,6 +15778,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15509,6 +15949,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15671,6 +16116,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15689,7 +16139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15762,6 +16212,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-050.xlsx
+++ b/stories/arbres/TREE-SEC-050.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Hugo est avec maman, à la ferme. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo écoute maman. Hugo entend les mots : feu vert, main, adulte, trottoir en attendant.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1877,6 +1885,7 @@
           <t>narrateur|Que fait-on ? Attendre le feu vert avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2052,6 +2061,7 @@
           <t>narrateur|Oui. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo respire. Hugo retient : feu vert, main, adulte, trottoir en attendant. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2243,6 +2253,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2414,6 +2425,7 @@
           <t>narrateur|Hugo a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2609,6 +2621,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2780,6 +2793,7 @@
           <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2947,6 +2961,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3118,6 +3133,7 @@
           <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3285,6 +3301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3456,6 +3473,7 @@
           <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3623,6 +3641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3794,6 +3813,7 @@
           <t>narrateur|Hugo a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3989,6 +4009,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4160,6 +4181,7 @@
           <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4327,6 +4349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4498,6 +4521,7 @@
           <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4665,6 +4689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4836,6 +4861,7 @@
           <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5003,6 +5029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5174,6 +5201,7 @@
           <t>narrateur|Hugo a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5369,6 +5397,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5540,6 +5569,7 @@
           <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5707,6 +5737,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5878,6 +5909,7 @@
           <t>narrateur|Hugo rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6045,6 +6077,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6216,6 +6249,7 @@
           <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6383,6 +6417,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6555,6 +6590,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6746,6 +6782,7 @@
           <t>narrateur|Que fait-on ? Attendre le feu vert avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6921,6 +6958,7 @@
           <t>narrateur|Oui. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo respire. Hugo retient : feu vert, main, adulte, trottoir en attendant. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7112,6 +7150,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7283,6 +7322,7 @@
           <t>narrateur|Hugo a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7478,6 +7518,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7649,6 +7690,7 @@
           <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7816,6 +7858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7987,6 +8030,7 @@
           <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8154,6 +8198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8325,6 +8370,7 @@
           <t>narrateur|Hugo rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8492,6 +8538,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8663,6 +8710,7 @@
           <t>narrateur|Hugo a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8858,6 +8906,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9029,6 +9078,7 @@
           <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9196,6 +9246,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9367,6 +9418,7 @@
           <t>narrateur|Hugo rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9534,6 +9586,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9705,6 +9758,7 @@
           <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9872,6 +9926,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10043,6 +10098,7 @@
           <t>narrateur|Hugo a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10238,6 +10294,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10409,6 +10466,7 @@
           <t>narrateur|Hugo rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10576,6 +10634,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10747,6 +10806,7 @@
           <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10914,6 +10974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11085,6 +11146,7 @@
           <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11252,6 +11314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11424,6 +11487,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11615,6 +11679,7 @@
           <t>narrateur|Que fait-on ? Attendre le feu vert avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11790,6 +11855,7 @@
           <t>narrateur|Oui. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo respire. Hugo retient : feu vert, main, adulte, trottoir en attendant. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11981,6 +12047,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12152,6 +12219,7 @@
           <t>narrateur|Hugo a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12347,6 +12415,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12518,6 +12587,7 @@
           <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12685,6 +12755,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12856,6 +12927,7 @@
           <t>narrateur|Hugo rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13023,6 +13095,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13194,6 +13267,7 @@
           <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13361,6 +13435,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13532,6 +13607,7 @@
           <t>narrateur|Hugo a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13727,6 +13803,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13898,6 +13975,7 @@
           <t>narrateur|Hugo rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14065,6 +14143,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14236,6 +14315,7 @@
           <t>narrateur|Hugo rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14403,6 +14483,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14574,6 +14655,7 @@
           <t>narrateur|Hugo rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14741,6 +14823,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14912,6 +14995,7 @@
           <t>narrateur|Hugo a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo répète tout bas : feu vert, main, adulte, trottoir en attendant. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15107,6 +15191,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15278,6 +15363,7 @@
           <t>narrateur|Hugo rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15445,6 +15531,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15616,6 +15703,7 @@
           <t>narrateur|Hugo rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15783,6 +15871,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15954,6 +16043,7 @@
           <t>narrateur|Hugo rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Attendre le feu vert avec l'adulte. Voici le geste : attendre le feu vert ; donner la main ; avancer avec l'adulte. Hugo a entendu : feu vert, main, adulte, trottoir en attendant. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16121,6 +16211,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16139,7 +16230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16219,6 +16310,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16233,7 +16338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16420,6 +16525,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
